--- a/data/demo/Югоцентр бригады.xlsx
+++ b/data/demo/Югоцентр бригады.xlsx
@@ -464,7 +464,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Винокурова, д. 12 к 4</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -482,7 +486,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Большая Серпуховская, д. 64</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -500,7 +508,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Кедрова, д. 16 к 1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -518,7 +530,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Трофимова, д. 8А</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -536,7 +552,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Каховка, д. 17/14</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -554,7 +574,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Судостроительная, д. 32</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -572,7 +596,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Город Москва, пр-кт.Севастопольский, д. 32</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -590,7 +618,11 @@
           <t>Ремонт, Подключение и дозаказ, Аварии</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Винокурова, д. 10 к 1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -608,7 +640,11 @@
           <t>Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Погодинская, д. 12А</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -626,7 +662,11 @@
           <t>Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Коломенская, д. 1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -644,7 +684,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Город Москва, пр-кт.Андропова, д. 13/32</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
